--- a/docs/PRAP_Programming_Specification_v1.38.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.38.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.67.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
+          <t>PRAP_Development_Plan_v2.68.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Read directly from PRAP_Development_Plan_v2.67.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
+          <t>Read directly from PRAP_Development_Plan_v2.68.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.67.xlsx</t>
+          <t>PRAP_Development_Plan_v2.68.xlsx</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">

--- a/docs/PRAP_Programming_Specification_v1.38.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.38.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.68.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
+          <t>PRAP_Development_Plan_v2.69.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Read directly from PRAP_Development_Plan_v2.68.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
+          <t>Read directly from PRAP_Development_Plan_v2.69.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.68.xlsx</t>
+          <t>PRAP_Development_Plan_v2.69.xlsx</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
